--- a/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.66%830,000</t>
+          <t>9.88%851,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.66%</t>
+          <t>9.88%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>830000</v>
+        <v>851000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1040</v>
+        <v>989</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.00%1,197,000</t>
+          <t>5.94%1,227,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>5.94%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1197000</v>
+        <v>1227000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,34 +626,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5010</v>
+        <v>3095</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.75%238,000</t>
+          <t>5.82%384,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5.82%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>238000</v>
+        <v>384000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3105</v>
+        <v>4675</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.61%375,000</t>
+          <t>5.59%244,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>375000</v>
+        <v>244000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,33 +753,33 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4045</v>
+        <v>3915</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.25%269,000</t>
+          <t>5.29%276,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>269000</v>
+        <v>276000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7640</v>
+        <v>7635</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.71%128,000</t>
+          <t>4.90%131,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>128000</v>
+        <v>131000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1250</v>
+        <v>6315</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.66%608,000</t>
+          <t>3.68%119,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>608000</v>
+        <v>119000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6405</v>
+        <v>1190</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.58%116,000</t>
+          <t>3.63%623,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>116000</v>
+        <v>623000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,33 +997,33 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.13%952,000</t>
+          <t>3.19%976,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>952000</v>
+        <v>976000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.19%312</t>
+          <t>-5.13%296</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.00%1,995,000</t>
+          <t>2.96%2,045,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1995000</v>
+        <v>2045000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,20 +1119,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1885</v>
+        <v>1810</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.43%267,644</t>
+          <t>2.43%274,644</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>267644</v>
+        <v>274644</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>543</v>
+        <v>1625</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.34%895,000</t>
+          <t>2.27%285,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>895000</v>
+        <v>285000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-7.55%502</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1480</v>
+        <v>502</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.30%323,000</t>
+          <t>2.26%918,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>323000</v>
+        <v>918000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1705</v>
+        <v>4610</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.28%278,000</t>
+          <t>2.17%96,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>278000</v>
+        <v>96000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:53</t>
+          <t>2026-10-30 23:09:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4840</v>
+        <v>1335</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.19%94,000</t>
+          <t>2.16%331,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>94000</v>
+        <v>331000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,33 +1424,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1390</v>
+        <v>1265</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.07%309,000</t>
+          <t>1.96%317,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>309000</v>
+        <v>317000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,33 +1485,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9880</v>
+        <v>9650</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.91%40,000</t>
+          <t>1.94%41,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.19%2575</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2575</v>
+        <v>15970</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%153,000</t>
+          <t>1.87%23,900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>153000</v>
+        <v>23900</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-7.96%2370</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>16980</v>
+        <v>2370</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.87%22,900</t>
+          <t>1.82%157,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>22900</v>
+        <v>157000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,33 +1668,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1115</v>
+        <v>1020</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.80%335,000</t>
+          <t>1.71%343,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>335000</v>
+        <v>343000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,33 +1729,33 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%477</t>
+          <t>-4.72%454.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>477</v>
+        <v>454.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.62%706,000</t>
+          <t>1.61%724,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>706000</v>
+        <v>724000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,33 +1790,33 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.32%1260</t>
+          <t>-5.56%1190</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1260</v>
+        <v>1190</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.55%255,000</t>
+          <t>1.52%261,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>255000</v>
+        <v>261000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,33 +1851,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1755</v>
+        <v>1615</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.52%180,000</t>
+          <t>1.46%185,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>180000</v>
+        <v>185000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,33 +1912,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5815</v>
+        <v>5430</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.46%52,000</t>
+          <t>1.41%53,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,33 +1973,33 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.63%252</t>
+          <t>-4.56%240.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-4.56%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>252</v>
+        <v>240.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.41%1,160,000</t>
+          <t>1.40%1,189,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1160000</v>
+        <v>1189000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,34 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-2.08%2820</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1545</v>
+        <v>2820</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.33%179,000</t>
+          <t>1.34%97,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>179000</v>
+        <v>97000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-10%2880</t>
+          <t>-1.65%2385</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2880</v>
+        <v>2385</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.32%95,000</t>
+          <t>1.34%115,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>95000</v>
+        <v>115000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.42%2425</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2425</v>
+        <v>1435</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.31%112,000</t>
+          <t>1.29%184,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>112000</v>
+        <v>184000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2615萬海</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>+4.35%120</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>+4.35%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>188.5</v>
+        <v>120</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.09%1,198,000</t>
+          <t>1.11%1,897,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1198000</v>
+        <v>1897000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:54</t>
+          <t>2026-10-30 23:09:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.45%520</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>520</v>
+        <v>183.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.05%418,000</t>
+          <t>1.10%1,228,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>418000</v>
+        <v>1228000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,33 +2339,33 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.84%888</t>
+          <t>-2.36%867</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-2.36%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.04%243,000</t>
+          <t>1.06%249,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>243000</v>
+        <v>249000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2615萬海</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.95%115</t>
+          <t>-6.54%486</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-6.54%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>115</v>
+        <v>486</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.03%1,850,000</t>
+          <t>1.02%429,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1850000</v>
+        <v>429000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.42%1945</t>
+          <t>-2.11%1860</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1945</v>
+        <v>1860</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.98%105,000</t>
+          <t>0.97%107,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>105000</v>
+        <v>107000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.81%1900</t>
+          <t>-9.77%1755</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.81%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1900</v>
+        <v>1755</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.95%104,000</t>
+          <t>0.93%108,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>104000</v>
+        <v>108000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,20 +2583,20 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.33%596</t>
+          <t>-3.52%575</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.87%302,000</t>
+          <t>0.87%310,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>302000</v>
+        <v>310000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,33 +2644,33 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.73%1290</t>
+          <t>-2.71%1255</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.73%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1290</v>
+        <v>1255</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.84%135,000</t>
+          <t>0.85%138,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>135000</v>
+        <v>138000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,33 +2705,33 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.85%2000</t>
+          <t>-6%1880</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-6%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2000</v>
+        <v>1880</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.77%80,000</t>
+          <t>0.76%82,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>80000</v>
+        <v>82000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,33 +2766,33 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1%808</t>
+          <t>+0.25%810</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.67%171,000</t>
+          <t>0.69%175,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>171000</v>
+        <v>175000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,20 +2827,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>115.5</v>
+        <v>111.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.49%878,000</t>
+          <t>0.49%900,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>878000</v>
+        <v>900000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,20 +2888,20 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.69%213.5</t>
+          <t>-5.39%202</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-5.39%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>213.5</v>
+        <v>202</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.41%400,000</t>
+          <t>0.41%410,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>400000</v>
+        <v>410000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,20 +2949,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.17%294</t>
+          <t>-3.4%284</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.36%252,000</t>
+          <t>0.36%258,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>252000</v>
+        <v>258000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,20 +3010,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.33%1240</t>
+          <t>-4.03%1190</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-4.03%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1240</v>
+        <v>1190</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.35%59,000</t>
+          <t>0.35%60,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>59000</v>
+        <v>60000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.49%2050</t>
+          <t>-5.85%1930</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2050</v>
+        <v>1930</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.34%34,000</t>
+          <t>0.33%35,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>34000</v>
+        <v>35000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,20 +3132,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.41%362</t>
+          <t>-4.28%346.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>362</v>
+        <v>346.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.31%176,828</t>
+          <t>0.31%180,828</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>176828</v>
+        <v>180828</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:55</t>
+          <t>2026-10-30 23:09:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,33 +3193,33 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.24%841</t>
+          <t>-7.73%776</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-7.73%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%77,000</t>
+          <t>0.30%79,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>77000</v>
+        <v>79000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:57</t>
+          <t>2026-10-30 23:09:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,29 +3254,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.38%794</t>
+          <t>+1.13%803</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.26%69,000</t>
+          <t>0.28%71,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>69000</v>
+        <v>71000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:57</t>
+          <t>2026-10-30 23:09:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,33 +3315,33 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-9.77%1200</t>
+          <t>-9.58%1085</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-9.58%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1200</v>
+        <v>1085</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.26%45,000</t>
+          <t>0.24%46,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>45000</v>
+        <v>46000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:57</t>
+          <t>2026-10-30 23:09:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.61%551</t>
+          <t>+1.45%559</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.22%83,000</t>
+          <t>0.23%83,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:57</t>
+          <t>2026-10-30 23:09:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.87%170.5</t>
+          <t>-3.52%164.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>170.5</v>
+        <v>164.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:57</t>
+          <t>2026-10-30 23:09:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.88%1150</t>
+          <t>-6.52%1075</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1150</v>
+        <v>1075</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:06</t>
+          <t>2026-10-30 23:20:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:07</t>
+          <t>2026-10-30 23:20:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:08</t>
+          <t>2026-10-30 23:20:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:09</t>
+          <t>2026-10-30 23:20:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:09</t>
+          <t>2026-10-30 23:20:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:09</t>
+          <t>2026-10-30 23:20:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:09</t>
+          <t>2026-10-30 23:20:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:09:09</t>
+          <t>2026-10-30 23:20:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:48</t>
+          <t>2026-10-30 23:57:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:49</t>
+          <t>2026-10-30 23:57:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:51</t>
+          <t>2026-10-30 23:57:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:52</t>
+          <t>2026-10-30 23:57:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:52</t>
+          <t>2026-10-30 23:57:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:52</t>
+          <t>2026-10-30 23:57:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:52</t>
+          <t>2026-10-30 23:57:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:52</t>
+          <t>2026-10-30 23:57:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
